--- a/ДИТЯ22.xlsx
+++ b/ДИТЯ22.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxdxxdxx\Desktop\ds bot stalzone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C347C83-949C-4A91-8338-DC8544B52AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F509FBBB-2D74-44EC-9576-55B5F2901249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="83">
   <si>
     <t>Красивая таблица: только ники. Discord — /add в боте или лист tech.</t>
   </si>
@@ -45,223 +45,232 @@
     <t>Exterminat</t>
   </si>
   <si>
+    <t>Kyrma</t>
+  </si>
+  <si>
+    <t>X_ziligrizlik_X</t>
+  </si>
+  <si>
+    <t>__kiritoAvrom__</t>
+  </si>
+  <si>
+    <t>extanz</t>
+  </si>
+  <si>
+    <t>Ilosty</t>
+  </si>
+  <si>
+    <t>Ilya_Dyhovniy</t>
+  </si>
+  <si>
+    <t>PAPAtoyZAKALKI</t>
+  </si>
+  <si>
+    <t>лысый_дмитрий</t>
+  </si>
+  <si>
+    <t>grizlik</t>
+  </si>
+  <si>
+    <t>Стальной_алекс</t>
+  </si>
+  <si>
+    <t>Ender_hun</t>
+  </si>
+  <si>
+    <t>Пельмешек</t>
+  </si>
+  <si>
+    <t>meid</t>
+  </si>
+  <si>
+    <t>Felled</t>
+  </si>
+  <si>
+    <t>WTFO</t>
+  </si>
+  <si>
+    <t>Odi_um</t>
+  </si>
+  <si>
+    <t>stinkyyy</t>
+  </si>
+  <si>
+    <t>AHAHAHAHAHHA</t>
+  </si>
+  <si>
+    <t>zetka</t>
+  </si>
+  <si>
+    <t>Последний_миг</t>
+  </si>
+  <si>
+    <t>septemberburns</t>
+  </si>
+  <si>
+    <t>sosew</t>
+  </si>
+  <si>
+    <t>hard_d</t>
+  </si>
+  <si>
+    <t>JL_E_N_K_A</t>
+  </si>
+  <si>
+    <t>INK_invvi</t>
+  </si>
+  <si>
+    <t>nemass</t>
+  </si>
+  <si>
+    <t>treizy_</t>
+  </si>
+  <si>
+    <t>Abrovolga</t>
+  </si>
+  <si>
+    <t>лайфи</t>
+  </si>
+  <si>
+    <t>КТРЛ + S НЕ ЗАБЫВАЕМ</t>
+  </si>
+  <si>
+    <t>астэд</t>
+  </si>
+  <si>
+    <t>game_nick</t>
+  </si>
+  <si>
+    <t>discord_id</t>
+  </si>
+  <si>
+    <t>266906013486153728</t>
+  </si>
+  <si>
+    <t>960095949403877436</t>
+  </si>
+  <si>
+    <t>362176712483667968</t>
+  </si>
+  <si>
+    <t>946420453721907300</t>
+  </si>
+  <si>
+    <t>644219898905624616</t>
+  </si>
+  <si>
+    <t>556864039175716864</t>
+  </si>
+  <si>
+    <t>475756961191821335</t>
+  </si>
+  <si>
+    <t>621363278681079848</t>
+  </si>
+  <si>
+    <t>1153222608335151144</t>
+  </si>
+  <si>
+    <t>427586675821117463</t>
+  </si>
+  <si>
+    <t>430027249803198474</t>
+  </si>
+  <si>
+    <t>400036348066791424</t>
+  </si>
+  <si>
+    <t>871286150705328158</t>
+  </si>
+  <si>
+    <t>482511412120256563</t>
+  </si>
+  <si>
+    <t>iovecuit</t>
+  </si>
+  <si>
+    <t>1046146825637331015</t>
+  </si>
+  <si>
+    <t>JI_E_N_K_A</t>
+  </si>
+  <si>
+    <t>960210231298777139</t>
+  </si>
+  <si>
+    <t>Kaiffolom</t>
+  </si>
+  <si>
+    <t>300543285431107584</t>
+  </si>
+  <si>
+    <t>777158939980464169</t>
+  </si>
+  <si>
+    <t>684454713491718168</t>
+  </si>
+  <si>
+    <t>587541434085801993</t>
+  </si>
+  <si>
+    <t>298855160677924864</t>
+  </si>
+  <si>
+    <t>328067928161517569</t>
+  </si>
+  <si>
+    <t>240853680805511169</t>
+  </si>
+  <si>
     <t>shadowsghosts</t>
   </si>
   <si>
-    <t>X_ziligrizlik_X</t>
-  </si>
-  <si>
-    <t>__kiritoAvrom__</t>
-  </si>
-  <si>
-    <t>extanz</t>
-  </si>
-  <si>
-    <t>Ilosty</t>
-  </si>
-  <si>
-    <t>Ilya_Dyhovniy</t>
+    <t>608168547692183562</t>
+  </si>
+  <si>
+    <t>981519195512647680</t>
+  </si>
+  <si>
+    <t>288611869948641280</t>
+  </si>
+  <si>
+    <t>474955380766801921</t>
+  </si>
+  <si>
+    <t>958710987811356732</t>
+  </si>
+  <si>
+    <t>1437864200742502420</t>
+  </si>
+  <si>
+    <t>515586561929379841</t>
+  </si>
+  <si>
+    <t>1262022746909573171</t>
+  </si>
+  <si>
+    <t>1008349618473545799</t>
+  </si>
+  <si>
+    <t>431097360576282646</t>
+  </si>
+  <si>
+    <t>430687056021291009</t>
+  </si>
+  <si>
+    <t>424531635468369920</t>
+  </si>
+  <si>
+    <t>419142160773021697</t>
   </si>
   <si>
     <t>Свободовец_олег</t>
   </si>
   <si>
-    <t>лысый_дмитрий</t>
-  </si>
-  <si>
-    <t>sosew</t>
-  </si>
-  <si>
-    <t>grizlik</t>
-  </si>
-  <si>
-    <t>Стальной_алекс</t>
-  </si>
-  <si>
-    <t>Пельмешек</t>
-  </si>
-  <si>
-    <t>meid</t>
-  </si>
-  <si>
-    <t>Felled</t>
-  </si>
-  <si>
-    <t>WTFO</t>
-  </si>
-  <si>
-    <t>Odi_um</t>
-  </si>
-  <si>
-    <t>stinkyyy</t>
-  </si>
-  <si>
-    <t>AHAHAHAHAHHA</t>
-  </si>
-  <si>
-    <t>zetka</t>
-  </si>
-  <si>
-    <t>septemberburns</t>
-  </si>
-  <si>
-    <t>астэд</t>
-  </si>
-  <si>
-    <t>hard_d</t>
-  </si>
-  <si>
-    <t>PAPAtoyZAKALKI</t>
-  </si>
-  <si>
-    <t>INK_invvi</t>
-  </si>
-  <si>
-    <t>nemass</t>
-  </si>
-  <si>
-    <t>treizy_</t>
-  </si>
-  <si>
-    <t>Abrovolga</t>
-  </si>
-  <si>
-    <t>лайфи</t>
-  </si>
-  <si>
-    <t>КТРЛ + S НЕ ЗАБЫВАЕМ</t>
-  </si>
-  <si>
-    <t>Kaiffolom</t>
-  </si>
-  <si>
-    <t>iovecuit</t>
-  </si>
-  <si>
-    <t>game_nick</t>
-  </si>
-  <si>
-    <t>discord_id</t>
-  </si>
-  <si>
-    <t>266906013486153728</t>
-  </si>
-  <si>
-    <t>960095949403877436</t>
-  </si>
-  <si>
-    <t>362176712483667968</t>
-  </si>
-  <si>
-    <t>946420453721907300</t>
-  </si>
-  <si>
-    <t>644219898905624616</t>
-  </si>
-  <si>
-    <t>475756961191821335</t>
-  </si>
-  <si>
-    <t>621363278681079848</t>
-  </si>
-  <si>
-    <t>1153222608335151144</t>
-  </si>
-  <si>
-    <t>427586675821117463</t>
-  </si>
-  <si>
-    <t>430027249803198474</t>
-  </si>
-  <si>
-    <t>400036348066791424</t>
-  </si>
-  <si>
-    <t>871286150705328158</t>
-  </si>
-  <si>
-    <t>482511412120256563</t>
-  </si>
-  <si>
-    <t>1046146825637331015</t>
-  </si>
-  <si>
-    <t>300543285431107584</t>
-  </si>
-  <si>
-    <t>684454713491718168</t>
-  </si>
-  <si>
-    <t>587541434085801993</t>
-  </si>
-  <si>
-    <t>298855160677924864</t>
-  </si>
-  <si>
-    <t>328067928161517569</t>
-  </si>
-  <si>
-    <t>240853680805511169</t>
-  </si>
-  <si>
-    <t>608168547692183562</t>
-  </si>
-  <si>
-    <t>981519195512647680</t>
-  </si>
-  <si>
-    <t>288611869948641280</t>
-  </si>
-  <si>
-    <t>474955380766801921</t>
-  </si>
-  <si>
-    <t>958710987811356732</t>
-  </si>
-  <si>
-    <t>1437864200742502420</t>
-  </si>
-  <si>
-    <t>515586561929379841</t>
-  </si>
-  <si>
-    <t>1262022746909573171</t>
-  </si>
-  <si>
-    <t>1008349618473545799</t>
-  </si>
-  <si>
-    <t>431097360576282646</t>
-  </si>
-  <si>
-    <t>430687056021291009</t>
-  </si>
-  <si>
-    <t>424531635468369920</t>
-  </si>
-  <si>
-    <t>Последний_Миг</t>
-  </si>
-  <si>
-    <t>419142160773021697</t>
-  </si>
-  <si>
     <t>1160904279813533806</t>
   </si>
   <si>
     <t>512311478796156929</t>
-  </si>
-  <si>
-    <t>Последний_миг</t>
-  </si>
-  <si>
-    <t>Ender_hun</t>
-  </si>
-  <si>
-    <t>Kyrma</t>
-  </si>
-  <si>
-    <t>JL_E_N_K_A</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1062,7 @@
     </row>
     <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="11" t="s">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="D7" s="26" t="s">
         <v>8</v>
@@ -1073,22 +1082,24 @@
         <v>12</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F8" s="20" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="11"/>
+      <c r="C9" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="D9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="20" t="s">
         <v>17</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
@@ -1135,43 +1146,43 @@
         <v>25</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="F13" s="26"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14" s="26"/>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C15" s="9" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15" s="26"/>
     </row>
     <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F16" s="27"/>
     </row>
@@ -1201,7 +1212,7 @@
     </row>
     <row r="29" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1253,7 +1264,7 @@
     </row>
     <row r="8" spans="4:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D8" s="11" t="s">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>8</v>
@@ -1273,7 +1284,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>14</v>
@@ -1281,16 +1292,16 @@
     </row>
     <row r="10" spans="4:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="F10" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="G10" s="20" t="s">
         <v>17</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="11" spans="4:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1337,43 +1348,43 @@
         <v>25</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="G14" s="26"/>
     </row>
     <row r="15" spans="4:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G15" s="26"/>
     </row>
     <row r="16" spans="4:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D16" s="9" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G16" s="26"/>
     </row>
     <row r="17" spans="4:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G17" s="27"/>
     </row>
@@ -1396,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="10.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -1420,7 +1431,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>41</v>
@@ -1452,7 +1463,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>45</v>
@@ -1460,7 +1471,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>46</v>
@@ -1468,7 +1479,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>47</v>
@@ -1476,7 +1487,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>48</v>
@@ -1484,7 +1495,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>49</v>
@@ -1492,7 +1503,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>50</v>
@@ -1500,7 +1511,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>51</v>
@@ -1508,7 +1519,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>52</v>
@@ -1516,7 +1527,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>53</v>
@@ -1524,170 +1535,194 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
